--- a/data/trans_orig/IP22_R-Edad-trans_orig.xlsx
+++ b/data/trans_orig/IP22_R-Edad-trans_orig.xlsx
@@ -733,12 +733,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>25998</t>
+          <t>26090</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>40761</t>
+          <t>40963</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -748,12 +748,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>24,49%</t>
+          <t>24,57%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>38,39%</t>
+          <t>38,58%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -768,12 +768,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>26226</t>
+          <t>26296</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>42249</t>
+          <t>42160</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -783,12 +783,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>21,61%</t>
+          <t>21,66%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>34,81%</t>
+          <t>34,73%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>55704</t>
+          <t>55470</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>78043</t>
+          <t>78300</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -818,12 +818,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>24,48%</t>
+          <t>24,38%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>34,3%</t>
+          <t>34,41%</t>
         </is>
       </c>
     </row>
@@ -846,12 +846,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>65410</t>
+          <t>65208</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>80173</t>
+          <t>80081</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -861,12 +861,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>61,61%</t>
+          <t>61,42%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>75,51%</t>
+          <t>75,43%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -881,12 +881,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>79131</t>
+          <t>79220</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>95154</t>
+          <t>95084</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -896,12 +896,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>65,19%</t>
+          <t>65,27%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>78,39%</t>
+          <t>78,34%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>149508</t>
+          <t>149251</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>171847</t>
+          <t>172081</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -931,12 +931,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>65,7%</t>
+          <t>65,59%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>75,52%</t>
+          <t>75,62%</t>
         </is>
       </c>
     </row>
@@ -1076,12 +1076,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>41617</t>
+          <t>41086</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>62474</t>
+          <t>62047</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1091,12 +1091,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>16,44%</t>
+          <t>16,23%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>24,67%</t>
+          <t>24,5%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1111,12 +1111,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>57474</t>
+          <t>58545</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>80781</t>
+          <t>80581</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1126,12 +1126,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>22,65%</t>
+          <t>23,07%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>31,83%</t>
+          <t>31,76%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1146,12 +1146,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>103980</t>
+          <t>106307</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>135564</t>
+          <t>137160</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1161,12 +1161,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>20,51%</t>
+          <t>20,97%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>26,74%</t>
+          <t>27,06%</t>
         </is>
       </c>
     </row>
@@ -1189,12 +1189,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>190731</t>
+          <t>191158</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>211588</t>
+          <t>212119</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1204,12 +1204,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>75,33%</t>
+          <t>75,5%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>83,56%</t>
+          <t>83,77%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1224,12 +1224,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>172975</t>
+          <t>173175</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>196282</t>
+          <t>195211</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1239,12 +1239,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>68,17%</t>
+          <t>68,24%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>77,35%</t>
+          <t>76,93%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1259,12 +1259,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>371397</t>
+          <t>369801</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>402981</t>
+          <t>400654</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1274,12 +1274,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>73,26%</t>
+          <t>72,94%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>79,49%</t>
+          <t>79,03%</t>
         </is>
       </c>
     </row>
@@ -1419,12 +1419,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>15115</t>
+          <t>15554</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>28959</t>
+          <t>29050</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1434,12 +1434,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>11,85%</t>
+          <t>12,19%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>22,7%</t>
+          <t>22,78%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1454,12 +1454,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>14438</t>
+          <t>15025</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>27699</t>
+          <t>28334</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1469,12 +1469,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>10,2%</t>
+          <t>10,62%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>19,57%</t>
+          <t>20,02%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1489,12 +1489,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>33029</t>
+          <t>33504</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>52253</t>
+          <t>52936</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1504,12 +1504,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>12,28%</t>
+          <t>12,45%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>19,42%</t>
+          <t>19,67%</t>
         </is>
       </c>
     </row>
@@ -1532,12 +1532,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>98589</t>
+          <t>98498</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>112433</t>
+          <t>111994</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1547,12 +1547,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>77,3%</t>
+          <t>77,22%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>88,15%</t>
+          <t>87,81%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1567,12 +1567,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>113816</t>
+          <t>113181</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>127077</t>
+          <t>126490</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1582,12 +1582,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>80,43%</t>
+          <t>79,98%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>89,8%</t>
+          <t>89,38%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1602,12 +1602,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>216810</t>
+          <t>216127</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>236034</t>
+          <t>235559</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1617,12 +1617,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>80,58%</t>
+          <t>80,33%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>87,72%</t>
+          <t>87,55%</t>
         </is>
       </c>
     </row>
@@ -1762,12 +1762,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>19243</t>
+          <t>19564</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>34812</t>
+          <t>35898</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1777,12 +1777,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>9,91%</t>
+          <t>10,08%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>17,94%</t>
+          <t>18,5%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1797,12 +1797,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>26313</t>
+          <t>25810</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>43757</t>
+          <t>43123</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1812,12 +1812,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>12,77%</t>
+          <t>12,53%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>21,24%</t>
+          <t>20,93%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1832,12 +1832,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>48769</t>
+          <t>48174</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>72331</t>
+          <t>71644</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1847,12 +1847,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>12,19%</t>
+          <t>12,04%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>18,08%</t>
+          <t>17,9%</t>
         </is>
       </c>
     </row>
@@ -1875,12 +1875,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>159285</t>
+          <t>158199</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>174854</t>
+          <t>174533</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1890,12 +1890,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>82,06%</t>
+          <t>81,5%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>90,09%</t>
+          <t>89,92%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1910,12 +1910,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>162292</t>
+          <t>162926</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>179736</t>
+          <t>180239</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1925,12 +1925,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>78,76%</t>
+          <t>79,07%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>87,23%</t>
+          <t>87,47%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>327815</t>
+          <t>328502</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>351377</t>
+          <t>351972</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1960,12 +1960,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>81,92%</t>
+          <t>82,1%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>87,81%</t>
+          <t>87,96%</t>
         </is>
       </c>
     </row>
@@ -2105,12 +2105,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>114820</t>
+          <t>114811</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>148284</t>
+          <t>148370</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2125,7 +2125,7 @@
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>21,77%</t>
+          <t>21,79%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2140,12 +2140,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>139843</t>
+          <t>140014</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>175288</t>
+          <t>175099</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2155,12 +2155,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>19,35%</t>
+          <t>19,37%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>24,25%</t>
+          <t>24,23%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2175,12 +2175,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>264539</t>
+          <t>264161</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>311881</t>
+          <t>315664</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2190,12 +2190,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>18,85%</t>
+          <t>18,82%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>22,22%</t>
+          <t>22,49%</t>
         </is>
       </c>
     </row>
@@ -2218,12 +2218,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>532737</t>
+          <t>532651</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>566201</t>
+          <t>566210</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2233,7 +2233,7 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>78,23%</t>
+          <t>78,21%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
@@ -2253,12 +2253,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>547412</t>
+          <t>547601</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>582857</t>
+          <t>582686</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2268,12 +2268,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>75,75%</t>
+          <t>75,77%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>80,65%</t>
+          <t>80,63%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2288,12 +2288,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>1091840</t>
+          <t>1088057</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>1139182</t>
+          <t>1139560</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2303,12 +2303,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>77,78%</t>
+          <t>77,51%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>81,15%</t>
+          <t>81,18%</t>
         </is>
       </c>
     </row>
@@ -2680,12 +2680,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>41211</t>
+          <t>40934</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>60060</t>
+          <t>59849</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -2695,12 +2695,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>28,08%</t>
+          <t>27,89%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>40,92%</t>
+          <t>40,78%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -2715,12 +2715,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>31717</t>
+          <t>31554</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>49637</t>
+          <t>48971</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -2730,12 +2730,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>21,96%</t>
+          <t>21,85%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>34,37%</t>
+          <t>33,91%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -2750,12 +2750,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>78494</t>
+          <t>79062</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>104496</t>
+          <t>103988</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -2765,12 +2765,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>26,96%</t>
+          <t>27,15%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>35,89%</t>
+          <t>35,71%</t>
         </is>
       </c>
     </row>
@@ -2793,12 +2793,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>86701</t>
+          <t>86912</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>105550</t>
+          <t>105827</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -2808,12 +2808,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>59,08%</t>
+          <t>59,22%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>71,92%</t>
+          <t>72,11%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -2828,12 +2828,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>94797</t>
+          <t>95463</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>112717</t>
+          <t>112880</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -2843,12 +2843,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>65,63%</t>
+          <t>66,09%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>78,04%</t>
+          <t>78,15%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -2863,12 +2863,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>186699</t>
+          <t>187207</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>212701</t>
+          <t>212133</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -2878,12 +2878,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>64,11%</t>
+          <t>64,29%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>73,04%</t>
+          <t>72,85%</t>
         </is>
       </c>
     </row>
@@ -3023,12 +3023,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>63427</t>
+          <t>62938</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>88440</t>
+          <t>86707</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -3038,12 +3038,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>26,92%</t>
+          <t>26,71%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>37,54%</t>
+          <t>36,8%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -3058,12 +3058,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>83312</t>
+          <t>83149</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>109886</t>
+          <t>111148</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -3073,12 +3073,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>31,06%</t>
+          <t>31,0%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>40,96%</t>
+          <t>41,43%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -3093,12 +3093,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>154162</t>
+          <t>152512</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>189674</t>
+          <t>188413</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -3108,12 +3108,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>30,6%</t>
+          <t>30,27%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>37,64%</t>
+          <t>37,39%</t>
         </is>
       </c>
     </row>
@@ -3136,12 +3136,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>147165</t>
+          <t>148898</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>172178</t>
+          <t>172667</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -3151,12 +3151,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>62,46%</t>
+          <t>63,2%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>73,08%</t>
+          <t>73,29%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -3171,12 +3171,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>158363</t>
+          <t>157101</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>184937</t>
+          <t>185100</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -3186,12 +3186,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>59,04%</t>
+          <t>58,57%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>68,94%</t>
+          <t>69,0%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -3206,12 +3206,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>314180</t>
+          <t>315441</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>349692</t>
+          <t>351342</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -3221,12 +3221,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>62,36%</t>
+          <t>62,61%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>69,4%</t>
+          <t>69,73%</t>
         </is>
       </c>
     </row>
@@ -3366,12 +3366,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>15590</t>
+          <t>16112</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>30259</t>
+          <t>30551</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -3381,12 +3381,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>9,93%</t>
+          <t>10,26%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>19,27%</t>
+          <t>19,45%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -3401,12 +3401,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>20543</t>
+          <t>20109</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>36895</t>
+          <t>36779</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -3416,12 +3416,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>12,95%</t>
+          <t>12,68%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>23,27%</t>
+          <t>23,19%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -3436,12 +3436,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>40142</t>
+          <t>39295</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>61125</t>
+          <t>62263</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -3451,12 +3451,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>12,72%</t>
+          <t>12,45%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>19,37%</t>
+          <t>19,73%</t>
         </is>
       </c>
     </row>
@@ -3479,12 +3479,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>126784</t>
+          <t>126492</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>141453</t>
+          <t>140931</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -3494,12 +3494,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>80,73%</t>
+          <t>80,55%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>90,07%</t>
+          <t>89,74%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -3514,12 +3514,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>121676</t>
+          <t>121792</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>138028</t>
+          <t>138462</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -3529,12 +3529,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>76,73%</t>
+          <t>76,81%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>87,05%</t>
+          <t>87,32%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -3549,12 +3549,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>254489</t>
+          <t>253351</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>275472</t>
+          <t>276319</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -3564,12 +3564,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>80,63%</t>
+          <t>80,27%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>87,28%</t>
+          <t>87,55%</t>
         </is>
       </c>
     </row>
@@ -3709,12 +3709,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>13186</t>
+          <t>12549</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>26603</t>
+          <t>26130</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -3724,12 +3724,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>7,7%</t>
+          <t>7,32%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>15,53%</t>
+          <t>15,25%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -3744,12 +3744,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>33464</t>
+          <t>34538</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>52014</t>
+          <t>53068</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -3759,12 +3759,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>18,69%</t>
+          <t>19,28%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>29,04%</t>
+          <t>29,63%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -3779,12 +3779,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>50906</t>
+          <t>51132</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>74524</t>
+          <t>74286</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -3794,12 +3794,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>14,53%</t>
+          <t>14,59%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>21,27%</t>
+          <t>21,2%</t>
         </is>
       </c>
     </row>
@@ -3822,12 +3822,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>144734</t>
+          <t>145207</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>158151</t>
+          <t>158788</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -3837,12 +3837,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>84,47%</t>
+          <t>84,75%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>92,3%</t>
+          <t>92,68%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -3857,12 +3857,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>127084</t>
+          <t>126030</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>145634</t>
+          <t>144560</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -3872,12 +3872,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>70,96%</t>
+          <t>70,37%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>81,31%</t>
+          <t>80,72%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -3892,12 +3892,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>275911</t>
+          <t>276149</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>299529</t>
+          <t>299303</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -3907,12 +3907,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>78,73%</t>
+          <t>78,8%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>85,47%</t>
+          <t>85,41%</t>
         </is>
       </c>
     </row>
@@ -4052,12 +4052,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>149607</t>
+          <t>148063</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>187162</t>
+          <t>187006</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -4067,12 +4067,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>21,05%</t>
+          <t>20,83%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>26,33%</t>
+          <t>26,31%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -4087,12 +4087,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>187350</t>
+          <t>186934</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>228833</t>
+          <t>227835</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -4102,12 +4102,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>24,97%</t>
+          <t>24,91%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>30,5%</t>
+          <t>30,36%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -4122,12 +4122,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>346823</t>
+          <t>348333</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>404113</t>
+          <t>403716</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -4137,12 +4137,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>23,74%</t>
+          <t>23,84%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>27,66%</t>
+          <t>27,63%</t>
         </is>
       </c>
     </row>
@@ -4165,12 +4165,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>523584</t>
+          <t>523740</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>561139</t>
+          <t>562683</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -4180,12 +4180,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>73,67%</t>
+          <t>73,69%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>78,95%</t>
+          <t>79,17%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -4200,12 +4200,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>521519</t>
+          <t>522517</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>563002</t>
+          <t>563418</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -4215,12 +4215,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>69,5%</t>
+          <t>69,64%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>75,03%</t>
+          <t>75,09%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -4235,12 +4235,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>1056984</t>
+          <t>1057381</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>1114274</t>
+          <t>1112764</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -4250,12 +4250,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>72,34%</t>
+          <t>72,37%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>76,26%</t>
+          <t>76,16%</t>
         </is>
       </c>
     </row>
@@ -4627,12 +4627,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>21679</t>
+          <t>21845</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>36925</t>
+          <t>36462</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -4642,12 +4642,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>16,47%</t>
+          <t>16,59%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>28,05%</t>
+          <t>27,7%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -4662,12 +4662,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>17598</t>
+          <t>17103</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>32718</t>
+          <t>31896</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -4677,12 +4677,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>14,17%</t>
+          <t>13,77%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>26,35%</t>
+          <t>25,69%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -4697,12 +4697,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>43328</t>
+          <t>41675</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>64617</t>
+          <t>63469</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -4712,12 +4712,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>16,94%</t>
+          <t>16,29%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>25,26%</t>
+          <t>24,81%</t>
         </is>
       </c>
     </row>
@@ -4740,12 +4740,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>94729</t>
+          <t>95192</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>109975</t>
+          <t>109809</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -4755,12 +4755,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>71,95%</t>
+          <t>72,3%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>83,53%</t>
+          <t>83,41%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -4775,12 +4775,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>91446</t>
+          <t>92268</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>106566</t>
+          <t>107061</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -4790,12 +4790,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>73,65%</t>
+          <t>74,31%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>85,83%</t>
+          <t>86,23%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -4810,12 +4810,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>191201</t>
+          <t>192349</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>212490</t>
+          <t>214143</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -4825,12 +4825,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>74,74%</t>
+          <t>75,19%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>83,06%</t>
+          <t>83,71%</t>
         </is>
       </c>
     </row>
@@ -4970,12 +4970,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>36228</t>
+          <t>36289</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>54867</t>
+          <t>54775</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -4985,12 +4985,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>17,21%</t>
+          <t>17,24%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>26,06%</t>
+          <t>26,02%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -5005,12 +5005,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>33200</t>
+          <t>33997</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>53295</t>
+          <t>52168</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -5020,12 +5020,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>12,87%</t>
+          <t>13,17%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>20,65%</t>
+          <t>20,22%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -5040,12 +5040,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>74470</t>
+          <t>74172</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>101727</t>
+          <t>101160</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -5055,12 +5055,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>15,89%</t>
+          <t>15,83%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>21,71%</t>
+          <t>21,59%</t>
         </is>
       </c>
     </row>
@@ -5083,12 +5083,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>155650</t>
+          <t>155742</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>174289</t>
+          <t>174228</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -5098,12 +5098,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>73,94%</t>
+          <t>73,98%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>82,79%</t>
+          <t>82,76%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -5118,12 +5118,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>204766</t>
+          <t>205893</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>224861</t>
+          <t>224064</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -5133,12 +5133,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>79,35%</t>
+          <t>79,78%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>87,13%</t>
+          <t>86,83%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -5153,12 +5153,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>366851</t>
+          <t>367418</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>394108</t>
+          <t>394406</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -5168,12 +5168,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>78,29%</t>
+          <t>78,41%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>84,11%</t>
+          <t>84,17%</t>
         </is>
       </c>
     </row>
@@ -5313,12 +5313,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>23581</t>
+          <t>23052</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>39509</t>
+          <t>39498</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -5328,12 +5328,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>12,48%</t>
+          <t>12,2%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>20,92%</t>
+          <t>20,91%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -5348,12 +5348,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>22954</t>
+          <t>22796</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>40122</t>
+          <t>39939</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -5363,12 +5363,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>12,17%</t>
+          <t>12,09%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>21,28%</t>
+          <t>21,18%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -5383,12 +5383,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>50910</t>
+          <t>50393</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>74504</t>
+          <t>73726</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -5398,12 +5398,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>13,49%</t>
+          <t>13,35%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>19,74%</t>
+          <t>19,53%</t>
         </is>
       </c>
     </row>
@@ -5426,12 +5426,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>149390</t>
+          <t>149401</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>165318</t>
+          <t>165847</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -5441,12 +5441,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>79,08%</t>
+          <t>79,09%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>87,52%</t>
+          <t>87,8%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -5461,12 +5461,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>148450</t>
+          <t>148633</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>165618</t>
+          <t>165776</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -5476,12 +5476,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>78,72%</t>
+          <t>78,82%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>87,83%</t>
+          <t>87,91%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -5496,12 +5496,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>302967</t>
+          <t>303745</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>326561</t>
+          <t>327078</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -5511,12 +5511,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>80,26%</t>
+          <t>80,47%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>86,51%</t>
+          <t>86,65%</t>
         </is>
       </c>
     </row>
@@ -5656,12 +5656,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>14036</t>
+          <t>12914</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>28356</t>
+          <t>26079</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -5671,12 +5671,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>8,1%</t>
+          <t>7,45%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>16,36%</t>
+          <t>15,05%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -5691,12 +5691,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>20014</t>
+          <t>19039</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>36638</t>
+          <t>35418</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -5706,12 +5706,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>11,55%</t>
+          <t>10,99%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>21,15%</t>
+          <t>20,45%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -5726,12 +5726,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>36944</t>
+          <t>37081</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>57590</t>
+          <t>58860</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -5741,12 +5741,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>10,66%</t>
+          <t>10,7%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>16,62%</t>
+          <t>16,99%</t>
         </is>
       </c>
     </row>
@@ -5769,12 +5769,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>144945</t>
+          <t>147222</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>159265</t>
+          <t>160387</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -5784,12 +5784,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>83,64%</t>
+          <t>84,95%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>91,9%</t>
+          <t>92,55%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -5804,12 +5804,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>136592</t>
+          <t>137812</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>153216</t>
+          <t>154191</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -5819,12 +5819,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>78,85%</t>
+          <t>79,55%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>88,45%</t>
+          <t>89,01%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -5839,12 +5839,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>288940</t>
+          <t>287670</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>309586</t>
+          <t>309449</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -5854,12 +5854,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>83,38%</t>
+          <t>83,01%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>89,34%</t>
+          <t>89,3%</t>
         </is>
       </c>
     </row>
@@ -5999,12 +5999,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>109625</t>
+          <t>108595</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>143203</t>
+          <t>140126</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -6014,12 +6014,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>15,56%</t>
+          <t>15,42%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>20,33%</t>
+          <t>19,89%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -6034,12 +6034,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>108303</t>
+          <t>108277</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>142659</t>
+          <t>141691</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -6049,12 +6049,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>14,56%</t>
+          <t>14,55%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>19,17%</t>
+          <t>19,04%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -6069,12 +6069,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>227897</t>
+          <t>224244</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>273282</t>
+          <t>271598</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -6084,12 +6084,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>15,73%</t>
+          <t>15,48%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>18,87%</t>
+          <t>18,75%</t>
         </is>
       </c>
     </row>
@@ -6112,12 +6112,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>561168</t>
+          <t>564245</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>594746</t>
+          <t>595776</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -6127,12 +6127,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>79,67%</t>
+          <t>80,11%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>84,44%</t>
+          <t>84,58%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -6147,12 +6147,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>601367</t>
+          <t>602335</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>635723</t>
+          <t>635749</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -6162,12 +6162,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>80,83%</t>
+          <t>80,96%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>85,44%</t>
+          <t>85,45%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -6182,12 +6182,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>1175115</t>
+          <t>1176799</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>1220500</t>
+          <t>1224153</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -6197,12 +6197,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>81,13%</t>
+          <t>81,25%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>84,27%</t>
+          <t>84,52%</t>
         </is>
       </c>
     </row>
@@ -6574,12 +6574,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>10646</t>
+          <t>11085</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>20866</t>
+          <t>20783</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -6589,12 +6589,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>18,51%</t>
+          <t>19,27%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>36,28%</t>
+          <t>36,14%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -6609,12 +6609,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>8506</t>
+          <t>8484</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>19256</t>
+          <t>19442</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -6624,12 +6624,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>13,84%</t>
+          <t>13,81%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>31,34%</t>
+          <t>31,64%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -6644,12 +6644,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>21775</t>
+          <t>21311</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>35862</t>
+          <t>36105</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -6659,12 +6659,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>18,31%</t>
+          <t>17,92%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>30,15%</t>
+          <t>30,35%</t>
         </is>
       </c>
     </row>
@@ -6687,12 +6687,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>36645</t>
+          <t>36728</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>46865</t>
+          <t>46426</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -6702,12 +6702,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>63,72%</t>
+          <t>63,86%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>81,49%</t>
+          <t>80,73%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -6722,12 +6722,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>42188</t>
+          <t>42002</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>52938</t>
+          <t>52960</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -6737,12 +6737,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>68,66%</t>
+          <t>68,36%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>86,16%</t>
+          <t>86,19%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -6757,12 +6757,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>83093</t>
+          <t>82850</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>97180</t>
+          <t>97644</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -6772,12 +6772,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>69,85%</t>
+          <t>69,65%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>81,69%</t>
+          <t>82,08%</t>
         </is>
       </c>
     </row>
@@ -6917,12 +6917,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>16520</t>
+          <t>15788</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>31480</t>
+          <t>32046</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -6932,12 +6932,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>10,37%</t>
+          <t>9,91%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>19,76%</t>
+          <t>20,12%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -6952,12 +6952,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>22799</t>
+          <t>23305</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>42360</t>
+          <t>41606</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -6967,12 +6967,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>12,49%</t>
+          <t>12,77%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>23,2%</t>
+          <t>22,79%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -6987,12 +6987,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>41743</t>
+          <t>43275</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>66938</t>
+          <t>66350</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -7002,12 +7002,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>12,21%</t>
+          <t>12,66%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>19,58%</t>
+          <t>19,41%</t>
         </is>
       </c>
     </row>
@@ -7030,12 +7030,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>127819</t>
+          <t>127253</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>142779</t>
+          <t>143511</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -7045,12 +7045,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>80,24%</t>
+          <t>79,88%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>89,63%</t>
+          <t>90,09%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -7065,12 +7065,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>140194</t>
+          <t>140948</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>159755</t>
+          <t>159249</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -7080,12 +7080,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>76,8%</t>
+          <t>77,21%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>87,51%</t>
+          <t>87,23%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -7100,12 +7100,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>274915</t>
+          <t>275503</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>300110</t>
+          <t>298578</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -7115,12 +7115,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>80,42%</t>
+          <t>80,59%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>87,79%</t>
+          <t>87,34%</t>
         </is>
       </c>
     </row>
@@ -7260,12 +7260,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>18633</t>
+          <t>17635</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>34366</t>
+          <t>34170</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -7275,12 +7275,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>10,81%</t>
+          <t>10,23%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>19,94%</t>
+          <t>19,83%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -7295,12 +7295,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>25401</t>
+          <t>24148</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>46134</t>
+          <t>46178</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -7310,12 +7310,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>11,95%</t>
+          <t>11,36%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>21,71%</t>
+          <t>21,73%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -7330,12 +7330,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>48677</t>
+          <t>46732</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>73726</t>
+          <t>73312</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -7345,12 +7345,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>12,65%</t>
+          <t>12,14%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>19,16%</t>
+          <t>19,05%</t>
         </is>
       </c>
     </row>
@@ -7373,12 +7373,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>137983</t>
+          <t>138179</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>153716</t>
+          <t>154714</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -7388,12 +7388,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>80,06%</t>
+          <t>80,17%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>89,19%</t>
+          <t>89,77%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -7408,12 +7408,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>166356</t>
+          <t>166312</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>187089</t>
+          <t>188342</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -7423,12 +7423,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>78,29%</t>
+          <t>78,27%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>88,05%</t>
+          <t>88,64%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -7443,12 +7443,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>311113</t>
+          <t>311527</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>336162</t>
+          <t>338107</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -7458,12 +7458,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>80,84%</t>
+          <t>80,95%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>87,35%</t>
+          <t>87,86%</t>
         </is>
       </c>
     </row>
@@ -7603,12 +7603,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>26638</t>
+          <t>27373</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>55977</t>
+          <t>58827</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -7618,12 +7618,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>9,67%</t>
+          <t>9,94%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>20,32%</t>
+          <t>21,36%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -7638,12 +7638,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>27085</t>
+          <t>28203</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>50664</t>
+          <t>51951</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -7653,12 +7653,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>8,87%</t>
+          <t>9,23%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>16,58%</t>
+          <t>17,01%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -7673,12 +7673,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>59699</t>
+          <t>60603</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>98522</t>
+          <t>98741</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -7688,12 +7688,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>10,28%</t>
+          <t>10,43%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>16,96%</t>
+          <t>17,0%</t>
         </is>
       </c>
     </row>
@@ -7716,12 +7716,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>219481</t>
+          <t>216631</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>248820</t>
+          <t>248085</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -7731,12 +7731,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>79,68%</t>
+          <t>78,64%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>90,33%</t>
+          <t>90,06%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -7751,12 +7751,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>254819</t>
+          <t>253532</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>278398</t>
+          <t>277280</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -7766,12 +7766,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>83,42%</t>
+          <t>82,99%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>91,13%</t>
+          <t>90,77%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -7786,12 +7786,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>482418</t>
+          <t>482199</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>521241</t>
+          <t>520337</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -7801,12 +7801,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>83,04%</t>
+          <t>83,0%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>89,72%</t>
+          <t>89,57%</t>
         </is>
       </c>
     </row>
@@ -7946,12 +7946,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>84455</t>
+          <t>84008</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>123880</t>
+          <t>124638</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -7961,12 +7961,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>12,71%</t>
+          <t>12,64%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>18,64%</t>
+          <t>18,75%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -7981,12 +7981,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>99644</t>
+          <t>99617</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>138030</t>
+          <t>135313</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -7996,12 +7996,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>13,08%</t>
+          <t>13,07%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>18,11%</t>
+          <t>17,76%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -8016,12 +8016,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>196171</t>
+          <t>194422</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>251523</t>
+          <t>251730</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -8031,12 +8031,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>13,75%</t>
+          <t>13,63%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>17,63%</t>
+          <t>17,65%</t>
         </is>
       </c>
     </row>
@@ -8059,12 +8059,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>540737</t>
+          <t>539979</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>580162</t>
+          <t>580609</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -8074,12 +8074,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>81,36%</t>
+          <t>81,25%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>87,29%</t>
+          <t>87,36%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -8094,12 +8094,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>623942</t>
+          <t>626659</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>662328</t>
+          <t>662355</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -8109,12 +8109,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>81,89%</t>
+          <t>82,24%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>86,92%</t>
+          <t>86,93%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -8129,12 +8129,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>1175066</t>
+          <t>1174859</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>1230418</t>
+          <t>1232167</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -8144,12 +8144,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>82,37%</t>
+          <t>82,35%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>86,25%</t>
+          <t>86,37%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/IP22_R-Edad-trans_orig.xlsx
+++ b/data/trans_orig/IP22_R-Edad-trans_orig.xlsx
@@ -544,7 +544,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -555,7 +555,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -723,72 +723,72 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>33377</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>26102</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>41141</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>27,5%</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>21,5%</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>33,89%</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
           <t>52</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="K4" s="2" t="inlineStr">
         <is>
           <t>33143</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>26090</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>40963</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
+      <c r="L4" s="2" t="inlineStr">
+        <is>
+          <t>26185</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>41609</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
         <is>
           <t>31,22%</t>
         </is>
       </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>24,57%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>38,58%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
-      <c r="K4" s="2" t="inlineStr">
-        <is>
-          <t>33377</t>
-        </is>
-      </c>
-      <c r="L4" s="2" t="inlineStr">
-        <is>
-          <t>26296</t>
-        </is>
-      </c>
-      <c r="M4" s="2" t="inlineStr">
-        <is>
-          <t>42160</t>
-        </is>
-      </c>
-      <c r="N4" s="2" t="inlineStr">
-        <is>
-          <t>27,5%</t>
-        </is>
-      </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>21,66%</t>
+          <t>24,66%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>34,73%</t>
+          <t>39,19%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>55470</t>
+          <t>56852</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>78300</t>
+          <t>78758</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -818,12 +818,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>24,38%</t>
+          <t>24,98%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>34,41%</t>
+          <t>34,61%</t>
         </is>
       </c>
     </row>
@@ -836,72 +836,72 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>132</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>88003</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>80239</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>95278</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>72,5%</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>66,11%</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>78,5%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
           <t>110</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="K5" s="2" t="inlineStr">
         <is>
           <t>73028</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>65208</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>80081</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
+      <c r="L5" s="2" t="inlineStr">
+        <is>
+          <t>64562</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="inlineStr">
+        <is>
+          <t>79986</t>
+        </is>
+      </c>
+      <c r="N5" s="2" t="inlineStr">
         <is>
           <t>68,78%</t>
         </is>
       </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>61,42%</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>75,43%</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>132</t>
-        </is>
-      </c>
-      <c r="K5" s="2" t="inlineStr">
-        <is>
-          <t>88003</t>
-        </is>
-      </c>
-      <c r="L5" s="2" t="inlineStr">
-        <is>
-          <t>79220</t>
-        </is>
-      </c>
-      <c r="M5" s="2" t="inlineStr">
-        <is>
-          <t>95084</t>
-        </is>
-      </c>
-      <c r="N5" s="2" t="inlineStr">
-        <is>
-          <t>72,5%</t>
-        </is>
-      </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>65,27%</t>
+          <t>60,81%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>78,34%</t>
+          <t>75,34%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>149251</t>
+          <t>148793</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>172081</t>
+          <t>170699</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -931,12 +931,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>65,59%</t>
+          <t>65,39%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>75,62%</t>
+          <t>75,02%</t>
         </is>
       </c>
     </row>
@@ -949,57 +949,57 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>182</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>121380</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>121380</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>121380</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
           <t>162</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="K6" s="2" t="inlineStr">
         <is>
           <t>106171</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="L6" s="2" t="inlineStr">
         <is>
           <t>106171</t>
         </is>
       </c>
-      <c r="F6" s="2" t="inlineStr">
+      <c r="M6" s="2" t="inlineStr">
         <is>
           <t>106171</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>182</t>
-        </is>
-      </c>
-      <c r="K6" s="2" t="inlineStr">
-        <is>
-          <t>121380</t>
-        </is>
-      </c>
-      <c r="L6" s="2" t="inlineStr">
-        <is>
-          <t>121380</t>
-        </is>
-      </c>
-      <c r="M6" s="2" t="inlineStr">
-        <is>
-          <t>121380</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1066,72 +1066,72 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>103</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>68943</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>59115</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>80740</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>27,17%</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>23,3%</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>31,82%</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
           <t>78</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
+      <c r="K7" s="2" t="inlineStr">
         <is>
           <t>51262</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>41086</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>62047</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
+      <c r="L7" s="2" t="inlineStr">
+        <is>
+          <t>41214</t>
+        </is>
+      </c>
+      <c r="M7" s="2" t="inlineStr">
+        <is>
+          <t>61300</t>
+        </is>
+      </c>
+      <c r="N7" s="2" t="inlineStr">
         <is>
           <t>20,25%</t>
         </is>
       </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>16,23%</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>24,5%</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>103</t>
-        </is>
-      </c>
-      <c r="K7" s="2" t="inlineStr">
-        <is>
-          <t>68943</t>
-        </is>
-      </c>
-      <c r="L7" s="2" t="inlineStr">
-        <is>
-          <t>58545</t>
-        </is>
-      </c>
-      <c r="M7" s="2" t="inlineStr">
-        <is>
-          <t>80581</t>
-        </is>
-      </c>
-      <c r="N7" s="2" t="inlineStr">
-        <is>
-          <t>27,17%</t>
-        </is>
-      </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>23,07%</t>
+          <t>16,28%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>31,76%</t>
+          <t>24,21%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1146,12 +1146,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>106307</t>
+          <t>105164</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>137160</t>
+          <t>135389</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1161,12 +1161,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>20,97%</t>
+          <t>20,74%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>27,06%</t>
+          <t>26,71%</t>
         </is>
       </c>
     </row>
@@ -1179,72 +1179,72 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>279</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>184813</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>173016</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>194641</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>72,83%</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>68,18%</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>76,7%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
           <t>301</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="K8" s="2" t="inlineStr">
         <is>
           <t>201943</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>191158</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>212119</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
+      <c r="L8" s="2" t="inlineStr">
+        <is>
+          <t>191905</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="inlineStr">
+        <is>
+          <t>211991</t>
+        </is>
+      </c>
+      <c r="N8" s="2" t="inlineStr">
         <is>
           <t>79,75%</t>
         </is>
       </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>75,5%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>83,77%</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>279</t>
-        </is>
-      </c>
-      <c r="K8" s="2" t="inlineStr">
-        <is>
-          <t>184813</t>
-        </is>
-      </c>
-      <c r="L8" s="2" t="inlineStr">
-        <is>
-          <t>173175</t>
-        </is>
-      </c>
-      <c r="M8" s="2" t="inlineStr">
-        <is>
-          <t>195211</t>
-        </is>
-      </c>
-      <c r="N8" s="2" t="inlineStr">
-        <is>
-          <t>72,83%</t>
-        </is>
-      </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>68,24%</t>
+          <t>75,79%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>76,93%</t>
+          <t>83,72%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1259,12 +1259,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>369801</t>
+          <t>371572</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>400654</t>
+          <t>401797</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1274,12 +1274,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>72,94%</t>
+          <t>73,29%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>79,03%</t>
+          <t>79,26%</t>
         </is>
       </c>
     </row>
@@ -1292,57 +1292,57 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>382</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>253756</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>253756</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>253756</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
           <t>379</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
+      <c r="K9" s="2" t="inlineStr">
         <is>
           <t>253205</t>
         </is>
       </c>
-      <c r="E9" s="2" t="inlineStr">
+      <c r="L9" s="2" t="inlineStr">
         <is>
           <t>253205</t>
         </is>
       </c>
-      <c r="F9" s="2" t="inlineStr">
+      <c r="M9" s="2" t="inlineStr">
         <is>
           <t>253205</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>382</t>
-        </is>
-      </c>
-      <c r="K9" s="2" t="inlineStr">
-        <is>
-          <t>253756</t>
-        </is>
-      </c>
-      <c r="L9" s="2" t="inlineStr">
-        <is>
-          <t>253756</t>
-        </is>
-      </c>
-      <c r="M9" s="2" t="inlineStr">
-        <is>
-          <t>253756</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1409,72 +1409,72 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>31</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>20810</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>14911</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>28817</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>14,71%</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>10,54%</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>20,36%</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
           <t>32</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="K10" s="2" t="inlineStr">
         <is>
           <t>21108</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>15554</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>29050</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
+      <c r="L10" s="2" t="inlineStr">
+        <is>
+          <t>15041</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>28281</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="inlineStr">
         <is>
           <t>16,55%</t>
         </is>
       </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>12,19%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>22,78%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>31</t>
-        </is>
-      </c>
-      <c r="K10" s="2" t="inlineStr">
-        <is>
-          <t>20810</t>
-        </is>
-      </c>
-      <c r="L10" s="2" t="inlineStr">
-        <is>
-          <t>15025</t>
-        </is>
-      </c>
-      <c r="M10" s="2" t="inlineStr">
-        <is>
-          <t>28334</t>
-        </is>
-      </c>
-      <c r="N10" s="2" t="inlineStr">
-        <is>
-          <t>14,71%</t>
-        </is>
-      </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>10,62%</t>
+          <t>11,79%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>20,02%</t>
+          <t>22,17%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1489,12 +1489,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>33504</t>
+          <t>32711</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>52936</t>
+          <t>51522</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1504,12 +1504,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>12,45%</t>
+          <t>12,16%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>19,67%</t>
+          <t>19,15%</t>
         </is>
       </c>
     </row>
@@ -1522,72 +1522,72 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>181</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>120705</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>112698</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>126604</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>85,29%</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>79,64%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>89,46%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
           <t>159</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="K11" s="2" t="inlineStr">
         <is>
           <t>106440</t>
         </is>
       </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>98498</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>111994</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
+      <c r="L11" s="2" t="inlineStr">
+        <is>
+          <t>99267</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="inlineStr">
+        <is>
+          <t>112507</t>
+        </is>
+      </c>
+      <c r="N11" s="2" t="inlineStr">
         <is>
           <t>83,45%</t>
         </is>
       </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>77,22%</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>87,81%</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>181</t>
-        </is>
-      </c>
-      <c r="K11" s="2" t="inlineStr">
-        <is>
-          <t>120705</t>
-        </is>
-      </c>
-      <c r="L11" s="2" t="inlineStr">
-        <is>
-          <t>113181</t>
-        </is>
-      </c>
-      <c r="M11" s="2" t="inlineStr">
-        <is>
-          <t>126490</t>
-        </is>
-      </c>
-      <c r="N11" s="2" t="inlineStr">
-        <is>
-          <t>85,29%</t>
-        </is>
-      </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>79,98%</t>
+          <t>77,83%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>89,38%</t>
+          <t>88,21%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1602,12 +1602,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>216127</t>
+          <t>217541</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>235559</t>
+          <t>236352</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1617,12 +1617,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>80,33%</t>
+          <t>80,85%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>87,55%</t>
+          <t>87,84%</t>
         </is>
       </c>
     </row>
@@ -1635,57 +1635,57 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>212</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>141515</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>141515</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>141515</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
           <t>191</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="K12" s="2" t="inlineStr">
         <is>
           <t>127548</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
+      <c r="L12" s="2" t="inlineStr">
         <is>
           <t>127548</t>
         </is>
       </c>
-      <c r="F12" s="2" t="inlineStr">
+      <c r="M12" s="2" t="inlineStr">
         <is>
           <t>127548</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>212</t>
-        </is>
-      </c>
-      <c r="K12" s="2" t="inlineStr">
-        <is>
-          <t>141515</t>
-        </is>
-      </c>
-      <c r="L12" s="2" t="inlineStr">
-        <is>
-          <t>141515</t>
-        </is>
-      </c>
-      <c r="M12" s="2" t="inlineStr">
-        <is>
-          <t>141515</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1752,72 +1752,72 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>51</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>33899</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>26015</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>43766</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>16,45%</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>12,63%</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>21,24%</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
           <t>39</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
+      <c r="K13" s="2" t="inlineStr">
         <is>
           <t>26148</t>
         </is>
       </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>19564</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>35898</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
+      <c r="L13" s="2" t="inlineStr">
+        <is>
+          <t>19022</t>
+        </is>
+      </c>
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>34145</t>
+        </is>
+      </c>
+      <c r="N13" s="2" t="inlineStr">
         <is>
           <t>13,47%</t>
         </is>
       </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>10,08%</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>18,5%</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>51</t>
-        </is>
-      </c>
-      <c r="K13" s="2" t="inlineStr">
-        <is>
-          <t>33899</t>
-        </is>
-      </c>
-      <c r="L13" s="2" t="inlineStr">
-        <is>
-          <t>25810</t>
-        </is>
-      </c>
-      <c r="M13" s="2" t="inlineStr">
-        <is>
-          <t>43123</t>
-        </is>
-      </c>
-      <c r="N13" s="2" t="inlineStr">
-        <is>
-          <t>16,45%</t>
-        </is>
-      </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>12,53%</t>
+          <t>9,8%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>20,93%</t>
+          <t>17,59%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1832,12 +1832,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>48174</t>
+          <t>49081</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>71644</t>
+          <t>72200</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1847,12 +1847,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>12,04%</t>
+          <t>12,27%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>17,9%</t>
+          <t>18,04%</t>
         </is>
       </c>
     </row>
@@ -1865,72 +1865,72 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>259</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>172150</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>162283</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>180034</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>83,55%</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>78,76%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>87,37%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
           <t>247</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="K14" s="2" t="inlineStr">
         <is>
           <t>167949</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>158199</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>174533</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>159952</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr">
+        <is>
+          <t>175075</t>
+        </is>
+      </c>
+      <c r="N14" s="2" t="inlineStr">
         <is>
           <t>86,53%</t>
         </is>
       </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>81,5%</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>89,92%</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>259</t>
-        </is>
-      </c>
-      <c r="K14" s="2" t="inlineStr">
-        <is>
-          <t>172150</t>
-        </is>
-      </c>
-      <c r="L14" s="2" t="inlineStr">
-        <is>
-          <t>162926</t>
-        </is>
-      </c>
-      <c r="M14" s="2" t="inlineStr">
-        <is>
-          <t>180239</t>
-        </is>
-      </c>
-      <c r="N14" s="2" t="inlineStr">
-        <is>
-          <t>83,55%</t>
-        </is>
-      </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>79,07%</t>
+          <t>82,41%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>87,47%</t>
+          <t>90,2%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>328502</t>
+          <t>327946</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>351972</t>
+          <t>351065</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1960,12 +1960,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>82,1%</t>
+          <t>81,96%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>87,96%</t>
+          <t>87,73%</t>
         </is>
       </c>
     </row>
@@ -1978,57 +1978,57 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
+          <t>310</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>206049</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>206049</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>206049</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
           <t>286</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
+      <c r="K15" s="2" t="inlineStr">
         <is>
           <t>194097</t>
         </is>
       </c>
-      <c r="E15" s="2" t="inlineStr">
+      <c r="L15" s="2" t="inlineStr">
         <is>
           <t>194097</t>
         </is>
       </c>
-      <c r="F15" s="2" t="inlineStr">
+      <c r="M15" s="2" t="inlineStr">
         <is>
           <t>194097</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>310</t>
-        </is>
-      </c>
-      <c r="K15" s="2" t="inlineStr">
-        <is>
-          <t>206049</t>
-        </is>
-      </c>
-      <c r="L15" s="2" t="inlineStr">
-        <is>
-          <t>206049</t>
-        </is>
-      </c>
-      <c r="M15" s="2" t="inlineStr">
-        <is>
-          <t>206049</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -2095,72 +2095,72 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>235</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>157029</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>138749</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>177154</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>21,73%</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>19,2%</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>24,51%</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
           <t>201</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="K16" s="2" t="inlineStr">
         <is>
           <t>131661</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>114811</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>148370</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
+      <c r="L16" s="2" t="inlineStr">
+        <is>
+          <t>116201</t>
+        </is>
+      </c>
+      <c r="M16" s="2" t="inlineStr">
+        <is>
+          <t>149172</t>
+        </is>
+      </c>
+      <c r="N16" s="2" t="inlineStr">
         <is>
           <t>19,33%</t>
         </is>
       </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>16,86%</t>
-        </is>
-      </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>21,79%</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>235</t>
-        </is>
-      </c>
-      <c r="K16" s="2" t="inlineStr">
-        <is>
-          <t>157029</t>
-        </is>
-      </c>
-      <c r="L16" s="2" t="inlineStr">
-        <is>
-          <t>140014</t>
-        </is>
-      </c>
-      <c r="M16" s="2" t="inlineStr">
-        <is>
-          <t>175099</t>
-        </is>
-      </c>
-      <c r="N16" s="2" t="inlineStr">
-        <is>
-          <t>21,73%</t>
-        </is>
-      </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>19,37%</t>
+          <t>17,06%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>24,23%</t>
+          <t>21,9%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2175,12 +2175,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>264161</t>
+          <t>263954</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>315664</t>
+          <t>313393</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2190,12 +2190,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>18,82%</t>
+          <t>18,8%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>22,49%</t>
+          <t>22,33%</t>
         </is>
       </c>
     </row>
@@ -2208,72 +2208,72 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
+          <t>851</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>565671</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>545546</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>583951</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>78,27%</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>75,49%</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>80,8%</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
           <t>817</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
+      <c r="K17" s="2" t="inlineStr">
         <is>
           <t>549360</t>
         </is>
       </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>532651</t>
-        </is>
-      </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>566210</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
+      <c r="L17" s="2" t="inlineStr">
+        <is>
+          <t>531849</t>
+        </is>
+      </c>
+      <c r="M17" s="2" t="inlineStr">
+        <is>
+          <t>564820</t>
+        </is>
+      </c>
+      <c r="N17" s="2" t="inlineStr">
         <is>
           <t>80,67%</t>
         </is>
       </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>78,21%</t>
-        </is>
-      </c>
-      <c r="I17" s="2" t="inlineStr">
-        <is>
-          <t>83,14%</t>
-        </is>
-      </c>
-      <c r="J17" s="2" t="inlineStr">
-        <is>
-          <t>851</t>
-        </is>
-      </c>
-      <c r="K17" s="2" t="inlineStr">
-        <is>
-          <t>565671</t>
-        </is>
-      </c>
-      <c r="L17" s="2" t="inlineStr">
-        <is>
-          <t>547601</t>
-        </is>
-      </c>
-      <c r="M17" s="2" t="inlineStr">
-        <is>
-          <t>582686</t>
-        </is>
-      </c>
-      <c r="N17" s="2" t="inlineStr">
-        <is>
-          <t>78,27%</t>
-        </is>
-      </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>75,77%</t>
+          <t>78,1%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>80,63%</t>
+          <t>82,94%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2288,12 +2288,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>1088057</t>
+          <t>1090328</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>1139560</t>
+          <t>1139767</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2303,12 +2303,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>77,51%</t>
+          <t>77,67%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>81,18%</t>
+          <t>81,2%</t>
         </is>
       </c>
     </row>
@@ -2321,57 +2321,57 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>1086</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>722700</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>722700</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>722700</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
           <t>1018</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
+      <c r="K18" s="2" t="inlineStr">
         <is>
           <t>681021</t>
         </is>
       </c>
-      <c r="E18" s="2" t="inlineStr">
+      <c r="L18" s="2" t="inlineStr">
         <is>
           <t>681021</t>
         </is>
       </c>
-      <c r="F18" s="2" t="inlineStr">
+      <c r="M18" s="2" t="inlineStr">
         <is>
           <t>681021</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J18" s="2" t="inlineStr">
-        <is>
-          <t>1086</t>
-        </is>
-      </c>
-      <c r="K18" s="2" t="inlineStr">
-        <is>
-          <t>722700</t>
-        </is>
-      </c>
-      <c r="L18" s="2" t="inlineStr">
-        <is>
-          <t>722700</t>
-        </is>
-      </c>
-      <c r="M18" s="2" t="inlineStr">
-        <is>
-          <t>722700</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2491,7 +2491,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -2502,7 +2502,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -2670,72 +2670,72 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>59</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>40102</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>32047</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>49403</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>27,76%</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>22,19%</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>34,2%</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
           <t>76</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="K4" s="2" t="inlineStr">
         <is>
           <t>51020</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>40934</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>59849</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
+      <c r="L4" s="2" t="inlineStr">
+        <is>
+          <t>42814</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>60806</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
         <is>
           <t>34,76%</t>
         </is>
       </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>27,89%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>40,78%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>59</t>
-        </is>
-      </c>
-      <c r="K4" s="2" t="inlineStr">
-        <is>
-          <t>40102</t>
-        </is>
-      </c>
-      <c r="L4" s="2" t="inlineStr">
-        <is>
-          <t>31554</t>
-        </is>
-      </c>
-      <c r="M4" s="2" t="inlineStr">
-        <is>
-          <t>48971</t>
-        </is>
-      </c>
-      <c r="N4" s="2" t="inlineStr">
-        <is>
-          <t>27,76%</t>
-        </is>
-      </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>21,85%</t>
+          <t>29,17%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>33,91%</t>
+          <t>41,43%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -2750,12 +2750,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>79062</t>
+          <t>77313</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>103988</t>
+          <t>105656</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -2765,12 +2765,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>27,15%</t>
+          <t>26,55%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>35,71%</t>
+          <t>36,28%</t>
         </is>
       </c>
     </row>
@@ -2783,72 +2783,72 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>146</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>104332</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>95031</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>112387</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>72,24%</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>65,8%</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>77,81%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
           <t>143</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="K5" s="2" t="inlineStr">
         <is>
           <t>95741</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>86912</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>105827</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
+      <c r="L5" s="2" t="inlineStr">
+        <is>
+          <t>85955</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="inlineStr">
+        <is>
+          <t>103947</t>
+        </is>
+      </c>
+      <c r="N5" s="2" t="inlineStr">
         <is>
           <t>65,24%</t>
         </is>
       </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>59,22%</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>72,11%</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>146</t>
-        </is>
-      </c>
-      <c r="K5" s="2" t="inlineStr">
-        <is>
-          <t>104332</t>
-        </is>
-      </c>
-      <c r="L5" s="2" t="inlineStr">
-        <is>
-          <t>95463</t>
-        </is>
-      </c>
-      <c r="M5" s="2" t="inlineStr">
-        <is>
-          <t>112880</t>
-        </is>
-      </c>
-      <c r="N5" s="2" t="inlineStr">
-        <is>
-          <t>72,24%</t>
-        </is>
-      </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>66,09%</t>
+          <t>58,57%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>78,15%</t>
+          <t>70,83%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -2863,12 +2863,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>187207</t>
+          <t>185539</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>212133</t>
+          <t>213882</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -2878,12 +2878,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>64,29%</t>
+          <t>63,72%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>72,85%</t>
+          <t>73,45%</t>
         </is>
       </c>
     </row>
@@ -2896,57 +2896,57 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>205</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>144434</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>144434</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>144434</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
           <t>219</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="K6" s="2" t="inlineStr">
         <is>
           <t>146761</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="L6" s="2" t="inlineStr">
         <is>
           <t>146761</t>
         </is>
       </c>
-      <c r="F6" s="2" t="inlineStr">
+      <c r="M6" s="2" t="inlineStr">
         <is>
           <t>146761</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>205</t>
-        </is>
-      </c>
-      <c r="K6" s="2" t="inlineStr">
-        <is>
-          <t>144434</t>
-        </is>
-      </c>
-      <c r="L6" s="2" t="inlineStr">
-        <is>
-          <t>144434</t>
-        </is>
-      </c>
-      <c r="M6" s="2" t="inlineStr">
-        <is>
-          <t>144434</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -3013,72 +3013,72 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>132</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>96303</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>83388</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>109902</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>35,9%</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>31,09%</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>40,97%</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
           <t>107</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
+      <c r="K7" s="2" t="inlineStr">
         <is>
           <t>75294</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>62938</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>86707</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
+      <c r="L7" s="2" t="inlineStr">
+        <is>
+          <t>62921</t>
+        </is>
+      </c>
+      <c r="M7" s="2" t="inlineStr">
+        <is>
+          <t>86563</t>
+        </is>
+      </c>
+      <c r="N7" s="2" t="inlineStr">
         <is>
           <t>31,96%</t>
         </is>
       </c>
-      <c r="H7" s="2" t="inlineStr">
+      <c r="O7" s="2" t="inlineStr">
         <is>
           <t>26,71%</t>
         </is>
       </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>36,8%</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>132</t>
-        </is>
-      </c>
-      <c r="K7" s="2" t="inlineStr">
-        <is>
-          <t>96303</t>
-        </is>
-      </c>
-      <c r="L7" s="2" t="inlineStr">
-        <is>
-          <t>83149</t>
-        </is>
-      </c>
-      <c r="M7" s="2" t="inlineStr">
-        <is>
-          <t>111148</t>
-        </is>
-      </c>
-      <c r="N7" s="2" t="inlineStr">
-        <is>
-          <t>35,9%</t>
-        </is>
-      </c>
-      <c r="O7" s="2" t="inlineStr">
-        <is>
-          <t>31,0%</t>
-        </is>
-      </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>41,43%</t>
+          <t>36,74%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -3093,12 +3093,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>152512</t>
+          <t>153915</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>188413</t>
+          <t>189703</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -3108,12 +3108,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>30,27%</t>
+          <t>30,55%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>37,39%</t>
+          <t>37,65%</t>
         </is>
       </c>
     </row>
@@ -3126,74 +3126,74 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>241</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>171946</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>158347</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>184861</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>64,1%</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>59,03%</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>68,91%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
           <t>232</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="K8" s="2" t="inlineStr">
         <is>
           <t>160311</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>148898</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>172667</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
+      <c r="L8" s="2" t="inlineStr">
+        <is>
+          <t>149042</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="inlineStr">
+        <is>
+          <t>172684</t>
+        </is>
+      </c>
+      <c r="N8" s="2" t="inlineStr">
         <is>
           <t>68,04%</t>
         </is>
       </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>63,2%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
+      <c r="O8" s="2" t="inlineStr">
+        <is>
+          <t>63,26%</t>
+        </is>
+      </c>
+      <c r="P8" s="2" t="inlineStr">
         <is>
           <t>73,29%</t>
         </is>
       </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>241</t>
-        </is>
-      </c>
-      <c r="K8" s="2" t="inlineStr">
-        <is>
-          <t>171946</t>
-        </is>
-      </c>
-      <c r="L8" s="2" t="inlineStr">
-        <is>
-          <t>157101</t>
-        </is>
-      </c>
-      <c r="M8" s="2" t="inlineStr">
-        <is>
-          <t>185100</t>
-        </is>
-      </c>
-      <c r="N8" s="2" t="inlineStr">
-        <is>
-          <t>64,1%</t>
-        </is>
-      </c>
-      <c r="O8" s="2" t="inlineStr">
-        <is>
-          <t>58,57%</t>
-        </is>
-      </c>
-      <c r="P8" s="2" t="inlineStr">
-        <is>
-          <t>69,0%</t>
-        </is>
-      </c>
       <c r="Q8" s="2" t="inlineStr">
         <is>
           <t>473</t>
@@ -3206,12 +3206,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>315441</t>
+          <t>314151</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>351342</t>
+          <t>349939</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -3221,12 +3221,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>62,61%</t>
+          <t>62,35%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>69,73%</t>
+          <t>69,45%</t>
         </is>
       </c>
     </row>
@@ -3239,57 +3239,57 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>373</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>268249</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>268249</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>268249</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
           <t>339</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
+      <c r="K9" s="2" t="inlineStr">
         <is>
           <t>235605</t>
         </is>
       </c>
-      <c r="E9" s="2" t="inlineStr">
+      <c r="L9" s="2" t="inlineStr">
         <is>
           <t>235605</t>
         </is>
       </c>
-      <c r="F9" s="2" t="inlineStr">
+      <c r="M9" s="2" t="inlineStr">
         <is>
           <t>235605</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>373</t>
-        </is>
-      </c>
-      <c r="K9" s="2" t="inlineStr">
-        <is>
-          <t>268249</t>
-        </is>
-      </c>
-      <c r="L9" s="2" t="inlineStr">
-        <is>
-          <t>268249</t>
-        </is>
-      </c>
-      <c r="M9" s="2" t="inlineStr">
-        <is>
-          <t>268249</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -3356,72 +3356,72 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>38</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>27582</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>19939</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>36413</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>17,39%</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>12,57%</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>22,96%</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
           <t>32</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="K10" s="2" t="inlineStr">
         <is>
           <t>22629</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>16112</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>30551</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
+      <c r="L10" s="2" t="inlineStr">
+        <is>
+          <t>15899</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>30934</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="inlineStr">
         <is>
           <t>14,41%</t>
         </is>
       </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>10,26%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>19,45%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>38</t>
-        </is>
-      </c>
-      <c r="K10" s="2" t="inlineStr">
-        <is>
-          <t>27582</t>
-        </is>
-      </c>
-      <c r="L10" s="2" t="inlineStr">
-        <is>
-          <t>20109</t>
-        </is>
-      </c>
-      <c r="M10" s="2" t="inlineStr">
-        <is>
-          <t>36779</t>
-        </is>
-      </c>
-      <c r="N10" s="2" t="inlineStr">
-        <is>
-          <t>17,39%</t>
-        </is>
-      </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>12,68%</t>
+          <t>10,12%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>23,19%</t>
+          <t>19,7%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -3436,12 +3436,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>39295</t>
+          <t>39918</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>62263</t>
+          <t>61036</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -3451,12 +3451,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>12,45%</t>
+          <t>12,65%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>19,73%</t>
+          <t>19,34%</t>
         </is>
       </c>
     </row>
@@ -3469,72 +3469,72 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>190</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>130989</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>122158</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>138632</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>82,61%</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>77,04%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>87,43%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
           <t>191</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="K11" s="2" t="inlineStr">
         <is>
           <t>134414</t>
         </is>
       </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>126492</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>140931</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
+      <c r="L11" s="2" t="inlineStr">
+        <is>
+          <t>126109</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="inlineStr">
+        <is>
+          <t>141144</t>
+        </is>
+      </c>
+      <c r="N11" s="2" t="inlineStr">
         <is>
           <t>85,59%</t>
         </is>
       </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>80,55%</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>89,74%</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>190</t>
-        </is>
-      </c>
-      <c r="K11" s="2" t="inlineStr">
-        <is>
-          <t>130989</t>
-        </is>
-      </c>
-      <c r="L11" s="2" t="inlineStr">
-        <is>
-          <t>121792</t>
-        </is>
-      </c>
-      <c r="M11" s="2" t="inlineStr">
-        <is>
-          <t>138462</t>
-        </is>
-      </c>
-      <c r="N11" s="2" t="inlineStr">
-        <is>
-          <t>82,61%</t>
-        </is>
-      </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>76,81%</t>
+          <t>80,3%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>87,32%</t>
+          <t>89,88%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -3549,12 +3549,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>253351</t>
+          <t>254578</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>276319</t>
+          <t>275696</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -3564,12 +3564,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>80,27%</t>
+          <t>80,66%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>87,55%</t>
+          <t>87,35%</t>
         </is>
       </c>
     </row>
@@ -3582,57 +3582,57 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>228</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>158571</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>158571</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>158571</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
           <t>223</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="K12" s="2" t="inlineStr">
         <is>
           <t>157043</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
+      <c r="L12" s="2" t="inlineStr">
         <is>
           <t>157043</t>
         </is>
       </c>
-      <c r="F12" s="2" t="inlineStr">
+      <c r="M12" s="2" t="inlineStr">
         <is>
           <t>157043</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>228</t>
-        </is>
-      </c>
-      <c r="K12" s="2" t="inlineStr">
-        <is>
-          <t>158571</t>
-        </is>
-      </c>
-      <c r="L12" s="2" t="inlineStr">
-        <is>
-          <t>158571</t>
-        </is>
-      </c>
-      <c r="M12" s="2" t="inlineStr">
-        <is>
-          <t>158571</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -3699,72 +3699,72 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>64</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>42830</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>33767</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>52126</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>23,91%</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>18,85%</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>29,1%</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
           <t>28</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
+      <c r="K13" s="2" t="inlineStr">
         <is>
           <t>18874</t>
         </is>
       </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>12549</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>26130</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
+      <c r="L13" s="2" t="inlineStr">
+        <is>
+          <t>12466</t>
+        </is>
+      </c>
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>26056</t>
+        </is>
+      </c>
+      <c r="N13" s="2" t="inlineStr">
         <is>
           <t>11,02%</t>
         </is>
       </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>7,32%</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>15,25%</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>64</t>
-        </is>
-      </c>
-      <c r="K13" s="2" t="inlineStr">
-        <is>
-          <t>42830</t>
-        </is>
-      </c>
-      <c r="L13" s="2" t="inlineStr">
-        <is>
-          <t>34538</t>
-        </is>
-      </c>
-      <c r="M13" s="2" t="inlineStr">
-        <is>
-          <t>53068</t>
-        </is>
-      </c>
-      <c r="N13" s="2" t="inlineStr">
-        <is>
-          <t>23,91%</t>
-        </is>
-      </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>19,28%</t>
+          <t>7,28%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>29,63%</t>
+          <t>15,21%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -3779,12 +3779,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>51132</t>
+          <t>50131</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>74286</t>
+          <t>72672</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -3794,12 +3794,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>14,59%</t>
+          <t>14,31%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>21,2%</t>
+          <t>20,74%</t>
         </is>
       </c>
     </row>
@@ -3812,72 +3812,72 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>200</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>136268</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>126972</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>145331</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>76,09%</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>70,9%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>81,15%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
           <t>215</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="K14" s="2" t="inlineStr">
         <is>
           <t>152463</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>145207</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>158788</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>145281</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr">
+        <is>
+          <t>158871</t>
+        </is>
+      </c>
+      <c r="N14" s="2" t="inlineStr">
         <is>
           <t>88,98%</t>
         </is>
       </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>84,75%</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>92,68%</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>200</t>
-        </is>
-      </c>
-      <c r="K14" s="2" t="inlineStr">
-        <is>
-          <t>136268</t>
-        </is>
-      </c>
-      <c r="L14" s="2" t="inlineStr">
-        <is>
-          <t>126030</t>
-        </is>
-      </c>
-      <c r="M14" s="2" t="inlineStr">
-        <is>
-          <t>144560</t>
-        </is>
-      </c>
-      <c r="N14" s="2" t="inlineStr">
-        <is>
-          <t>76,09%</t>
-        </is>
-      </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>70,37%</t>
+          <t>84,79%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>80,72%</t>
+          <t>92,72%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -3892,12 +3892,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>276149</t>
+          <t>277763</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>299303</t>
+          <t>300304</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -3907,12 +3907,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>78,8%</t>
+          <t>79,26%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>85,41%</t>
+          <t>85,69%</t>
         </is>
       </c>
     </row>
@@ -3925,57 +3925,57 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
+          <t>264</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>179098</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>179098</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>179098</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
           <t>243</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
+      <c r="K15" s="2" t="inlineStr">
         <is>
           <t>171337</t>
         </is>
       </c>
-      <c r="E15" s="2" t="inlineStr">
+      <c r="L15" s="2" t="inlineStr">
         <is>
           <t>171337</t>
         </is>
       </c>
-      <c r="F15" s="2" t="inlineStr">
+      <c r="M15" s="2" t="inlineStr">
         <is>
           <t>171337</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>264</t>
-        </is>
-      </c>
-      <c r="K15" s="2" t="inlineStr">
-        <is>
-          <t>179098</t>
-        </is>
-      </c>
-      <c r="L15" s="2" t="inlineStr">
-        <is>
-          <t>179098</t>
-        </is>
-      </c>
-      <c r="M15" s="2" t="inlineStr">
-        <is>
-          <t>179098</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -4042,72 +4042,72 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>293</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>206817</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>187656</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>230418</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>27,56%</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>25,01%</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>30,71%</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
           <t>243</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="K16" s="2" t="inlineStr">
         <is>
           <t>167818</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>148063</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>187006</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
+      <c r="L16" s="2" t="inlineStr">
+        <is>
+          <t>151095</t>
+        </is>
+      </c>
+      <c r="M16" s="2" t="inlineStr">
+        <is>
+          <t>186466</t>
+        </is>
+      </c>
+      <c r="N16" s="2" t="inlineStr">
         <is>
           <t>23,61%</t>
         </is>
       </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>20,83%</t>
-        </is>
-      </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>26,31%</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>293</t>
-        </is>
-      </c>
-      <c r="K16" s="2" t="inlineStr">
-        <is>
-          <t>206817</t>
-        </is>
-      </c>
-      <c r="L16" s="2" t="inlineStr">
-        <is>
-          <t>186934</t>
-        </is>
-      </c>
-      <c r="M16" s="2" t="inlineStr">
-        <is>
-          <t>227835</t>
-        </is>
-      </c>
-      <c r="N16" s="2" t="inlineStr">
-        <is>
-          <t>27,56%</t>
-        </is>
-      </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>24,91%</t>
+          <t>21,26%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>30,36%</t>
+          <t>26,24%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -4122,12 +4122,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>348333</t>
+          <t>349557</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>403716</t>
+          <t>404110</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -4137,12 +4137,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>23,84%</t>
+          <t>23,92%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>27,63%</t>
+          <t>27,66%</t>
         </is>
       </c>
     </row>
@@ -4155,72 +4155,72 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
+          <t>777</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>543535</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>519934</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>562696</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>72,44%</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>69,29%</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>74,99%</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
           <t>781</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
+      <c r="K17" s="2" t="inlineStr">
         <is>
           <t>542928</t>
         </is>
       </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>523740</t>
-        </is>
-      </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>562683</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
+      <c r="L17" s="2" t="inlineStr">
+        <is>
+          <t>524280</t>
+        </is>
+      </c>
+      <c r="M17" s="2" t="inlineStr">
+        <is>
+          <t>559651</t>
+        </is>
+      </c>
+      <c r="N17" s="2" t="inlineStr">
         <is>
           <t>76,39%</t>
         </is>
       </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>73,69%</t>
-        </is>
-      </c>
-      <c r="I17" s="2" t="inlineStr">
-        <is>
-          <t>79,17%</t>
-        </is>
-      </c>
-      <c r="J17" s="2" t="inlineStr">
-        <is>
-          <t>777</t>
-        </is>
-      </c>
-      <c r="K17" s="2" t="inlineStr">
-        <is>
-          <t>543535</t>
-        </is>
-      </c>
-      <c r="L17" s="2" t="inlineStr">
-        <is>
-          <t>522517</t>
-        </is>
-      </c>
-      <c r="M17" s="2" t="inlineStr">
-        <is>
-          <t>563418</t>
-        </is>
-      </c>
-      <c r="N17" s="2" t="inlineStr">
-        <is>
-          <t>72,44%</t>
-        </is>
-      </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>69,64%</t>
+          <t>73,76%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>75,09%</t>
+          <t>78,74%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -4235,12 +4235,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>1057381</t>
+          <t>1056987</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>1112764</t>
+          <t>1111540</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -4250,12 +4250,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>72,37%</t>
+          <t>72,34%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>76,16%</t>
+          <t>76,08%</t>
         </is>
       </c>
     </row>
@@ -4268,57 +4268,57 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>1070</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>750352</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>750352</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>750352</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
           <t>1024</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
+      <c r="K18" s="2" t="inlineStr">
         <is>
           <t>710746</t>
         </is>
       </c>
-      <c r="E18" s="2" t="inlineStr">
+      <c r="L18" s="2" t="inlineStr">
         <is>
           <t>710746</t>
         </is>
       </c>
-      <c r="F18" s="2" t="inlineStr">
+      <c r="M18" s="2" t="inlineStr">
         <is>
           <t>710746</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J18" s="2" t="inlineStr">
-        <is>
-          <t>1070</t>
-        </is>
-      </c>
-      <c r="K18" s="2" t="inlineStr">
-        <is>
-          <t>750352</t>
-        </is>
-      </c>
-      <c r="L18" s="2" t="inlineStr">
-        <is>
-          <t>750352</t>
-        </is>
-      </c>
-      <c r="M18" s="2" t="inlineStr">
-        <is>
-          <t>750352</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -4438,7 +4438,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -4449,7 +4449,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -4617,72 +4617,72 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>35</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>24016</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>17108</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>32454</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>19,34%</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>13,78%</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>26,14%</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
           <t>46</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="K4" s="2" t="inlineStr">
         <is>
           <t>28663</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>21845</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>36462</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
+      <c r="L4" s="2" t="inlineStr">
+        <is>
+          <t>22076</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>37120</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
         <is>
           <t>21,77%</t>
         </is>
       </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>16,59%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>27,7%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>35</t>
-        </is>
-      </c>
-      <c r="K4" s="2" t="inlineStr">
-        <is>
-          <t>24016</t>
-        </is>
-      </c>
-      <c r="L4" s="2" t="inlineStr">
-        <is>
-          <t>17103</t>
-        </is>
-      </c>
-      <c r="M4" s="2" t="inlineStr">
-        <is>
-          <t>31896</t>
-        </is>
-      </c>
-      <c r="N4" s="2" t="inlineStr">
-        <is>
-          <t>19,34%</t>
-        </is>
-      </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>13,77%</t>
+          <t>16,77%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>25,69%</t>
+          <t>28,19%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -4697,12 +4697,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>41675</t>
+          <t>42317</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>63469</t>
+          <t>63287</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -4712,12 +4712,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>16,29%</t>
+          <t>16,54%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>24,81%</t>
+          <t>24,74%</t>
         </is>
       </c>
     </row>
@@ -4730,72 +4730,72 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>152</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>100148</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>91710</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>107056</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>80,66%</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>73,86%</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>86,22%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
           <t>165</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="K5" s="2" t="inlineStr">
         <is>
           <t>102991</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>95192</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>109809</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
+      <c r="L5" s="2" t="inlineStr">
+        <is>
+          <t>94534</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="inlineStr">
+        <is>
+          <t>109578</t>
+        </is>
+      </c>
+      <c r="N5" s="2" t="inlineStr">
         <is>
           <t>78,23%</t>
         </is>
       </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>72,3%</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>83,41%</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>152</t>
-        </is>
-      </c>
-      <c r="K5" s="2" t="inlineStr">
-        <is>
-          <t>100148</t>
-        </is>
-      </c>
-      <c r="L5" s="2" t="inlineStr">
-        <is>
-          <t>92268</t>
-        </is>
-      </c>
-      <c r="M5" s="2" t="inlineStr">
-        <is>
-          <t>107061</t>
-        </is>
-      </c>
-      <c r="N5" s="2" t="inlineStr">
-        <is>
-          <t>80,66%</t>
-        </is>
-      </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>74,31%</t>
+          <t>71,81%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>86,23%</t>
+          <t>83,23%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -4810,12 +4810,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>192349</t>
+          <t>192531</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>214143</t>
+          <t>213501</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -4825,12 +4825,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>75,19%</t>
+          <t>75,26%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>83,71%</t>
+          <t>83,46%</t>
         </is>
       </c>
     </row>
@@ -4843,57 +4843,57 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>187</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>124164</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>124164</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>124164</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
           <t>211</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="K6" s="2" t="inlineStr">
         <is>
           <t>131654</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="L6" s="2" t="inlineStr">
         <is>
           <t>131654</t>
         </is>
       </c>
-      <c r="F6" s="2" t="inlineStr">
+      <c r="M6" s="2" t="inlineStr">
         <is>
           <t>131654</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>187</t>
-        </is>
-      </c>
-      <c r="K6" s="2" t="inlineStr">
-        <is>
-          <t>124164</t>
-        </is>
-      </c>
-      <c r="L6" s="2" t="inlineStr">
-        <is>
-          <t>124164</t>
-        </is>
-      </c>
-      <c r="M6" s="2" t="inlineStr">
-        <is>
-          <t>124164</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -4960,72 +4960,72 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>63</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>42209</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>33212</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>52116</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>16,36%</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>12,87%</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>20,2%</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
           <t>73</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
+      <c r="K7" s="2" t="inlineStr">
         <is>
           <t>45267</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>36289</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>54775</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
+      <c r="L7" s="2" t="inlineStr">
+        <is>
+          <t>36576</t>
+        </is>
+      </c>
+      <c r="M7" s="2" t="inlineStr">
+        <is>
+          <t>55254</t>
+        </is>
+      </c>
+      <c r="N7" s="2" t="inlineStr">
         <is>
           <t>21,5%</t>
         </is>
       </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>17,24%</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>26,02%</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>63</t>
-        </is>
-      </c>
-      <c r="K7" s="2" t="inlineStr">
-        <is>
-          <t>42209</t>
-        </is>
-      </c>
-      <c r="L7" s="2" t="inlineStr">
-        <is>
-          <t>33997</t>
-        </is>
-      </c>
-      <c r="M7" s="2" t="inlineStr">
-        <is>
-          <t>52168</t>
-        </is>
-      </c>
-      <c r="N7" s="2" t="inlineStr">
-        <is>
-          <t>16,36%</t>
-        </is>
-      </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>13,17%</t>
+          <t>17,37%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>20,22%</t>
+          <t>26,25%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -5040,12 +5040,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>74172</t>
+          <t>74894</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>101160</t>
+          <t>100368</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -5055,12 +5055,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>15,83%</t>
+          <t>15,98%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>21,59%</t>
+          <t>21,42%</t>
         </is>
       </c>
     </row>
@@ -5073,72 +5073,72 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>317</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>215852</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>205945</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>224849</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>83,64%</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>79,8%</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>87,13%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
           <t>259</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="K8" s="2" t="inlineStr">
         <is>
           <t>165250</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>155742</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>174228</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
+      <c r="L8" s="2" t="inlineStr">
+        <is>
+          <t>155263</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="inlineStr">
+        <is>
+          <t>173941</t>
+        </is>
+      </c>
+      <c r="N8" s="2" t="inlineStr">
         <is>
           <t>78,5%</t>
         </is>
       </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>73,98%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>82,76%</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>317</t>
-        </is>
-      </c>
-      <c r="K8" s="2" t="inlineStr">
-        <is>
-          <t>215852</t>
-        </is>
-      </c>
-      <c r="L8" s="2" t="inlineStr">
-        <is>
-          <t>205893</t>
-        </is>
-      </c>
-      <c r="M8" s="2" t="inlineStr">
-        <is>
-          <t>224064</t>
-        </is>
-      </c>
-      <c r="N8" s="2" t="inlineStr">
-        <is>
-          <t>83,64%</t>
-        </is>
-      </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>79,78%</t>
+          <t>73,75%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>86,83%</t>
+          <t>82,63%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -5153,12 +5153,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>367418</t>
+          <t>368210</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>394406</t>
+          <t>393684</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -5168,12 +5168,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>78,41%</t>
+          <t>78,58%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>84,17%</t>
+          <t>84,02%</t>
         </is>
       </c>
     </row>
@@ -5186,57 +5186,57 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>380</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>258061</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>258061</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>258061</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
           <t>332</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
+      <c r="K9" s="2" t="inlineStr">
         <is>
           <t>210517</t>
         </is>
       </c>
-      <c r="E9" s="2" t="inlineStr">
+      <c r="L9" s="2" t="inlineStr">
         <is>
           <t>210517</t>
         </is>
       </c>
-      <c r="F9" s="2" t="inlineStr">
+      <c r="M9" s="2" t="inlineStr">
         <is>
           <t>210517</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>380</t>
-        </is>
-      </c>
-      <c r="K9" s="2" t="inlineStr">
-        <is>
-          <t>258061</t>
-        </is>
-      </c>
-      <c r="L9" s="2" t="inlineStr">
-        <is>
-          <t>258061</t>
-        </is>
-      </c>
-      <c r="M9" s="2" t="inlineStr">
-        <is>
-          <t>258061</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -5303,72 +5303,72 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>43</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>30963</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>22459</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>40211</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>16,42%</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>11,91%</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>21,32%</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
           <t>46</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="K10" s="2" t="inlineStr">
         <is>
           <t>30604</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>23052</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>39498</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
+      <c r="L10" s="2" t="inlineStr">
+        <is>
+          <t>22985</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>39194</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="inlineStr">
         <is>
           <t>16,2%</t>
         </is>
       </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>12,2%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>20,91%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>43</t>
-        </is>
-      </c>
-      <c r="K10" s="2" t="inlineStr">
-        <is>
-          <t>30963</t>
-        </is>
-      </c>
-      <c r="L10" s="2" t="inlineStr">
-        <is>
-          <t>22796</t>
-        </is>
-      </c>
-      <c r="M10" s="2" t="inlineStr">
-        <is>
-          <t>39939</t>
-        </is>
-      </c>
-      <c r="N10" s="2" t="inlineStr">
-        <is>
-          <t>16,42%</t>
-        </is>
-      </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>12,09%</t>
+          <t>12,17%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>21,18%</t>
+          <t>20,75%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -5383,12 +5383,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>50393</t>
+          <t>49762</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>73726</t>
+          <t>73479</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -5398,12 +5398,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>13,35%</t>
+          <t>13,18%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>19,53%</t>
+          <t>19,47%</t>
         </is>
       </c>
     </row>
@@ -5416,72 +5416,72 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>220</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>157609</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>148361</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>166113</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>83,58%</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>78,68%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>88,09%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
           <t>226</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="K11" s="2" t="inlineStr">
         <is>
           <t>158295</t>
         </is>
       </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>149401</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>165847</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
+      <c r="L11" s="2" t="inlineStr">
+        <is>
+          <t>149705</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="inlineStr">
+        <is>
+          <t>165914</t>
+        </is>
+      </c>
+      <c r="N11" s="2" t="inlineStr">
         <is>
           <t>83,8%</t>
         </is>
       </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>79,09%</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>87,8%</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>220</t>
-        </is>
-      </c>
-      <c r="K11" s="2" t="inlineStr">
-        <is>
-          <t>157609</t>
-        </is>
-      </c>
-      <c r="L11" s="2" t="inlineStr">
-        <is>
-          <t>148633</t>
-        </is>
-      </c>
-      <c r="M11" s="2" t="inlineStr">
-        <is>
-          <t>165776</t>
-        </is>
-      </c>
-      <c r="N11" s="2" t="inlineStr">
-        <is>
-          <t>83,58%</t>
-        </is>
-      </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>78,82%</t>
+          <t>79,25%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>87,91%</t>
+          <t>87,83%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -5496,12 +5496,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>303745</t>
+          <t>303992</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>327078</t>
+          <t>327709</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -5511,12 +5511,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>80,47%</t>
+          <t>80,53%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>86,65%</t>
+          <t>86,82%</t>
         </is>
       </c>
     </row>
@@ -5529,57 +5529,57 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>263</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>188572</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>188572</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>188572</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
           <t>272</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="K12" s="2" t="inlineStr">
         <is>
           <t>188899</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
+      <c r="L12" s="2" t="inlineStr">
         <is>
           <t>188899</t>
         </is>
       </c>
-      <c r="F12" s="2" t="inlineStr">
+      <c r="M12" s="2" t="inlineStr">
         <is>
           <t>188899</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>263</t>
-        </is>
-      </c>
-      <c r="K12" s="2" t="inlineStr">
-        <is>
-          <t>188572</t>
-        </is>
-      </c>
-      <c r="L12" s="2" t="inlineStr">
-        <is>
-          <t>188572</t>
-        </is>
-      </c>
-      <c r="M12" s="2" t="inlineStr">
-        <is>
-          <t>188572</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -5646,72 +5646,72 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>37</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>27340</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>20087</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>35605</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>15,78%</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>11,6%</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>20,55%</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
           <t>29</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
+      <c r="K13" s="2" t="inlineStr">
         <is>
           <t>19550</t>
         </is>
       </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>12914</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>26079</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
+      <c r="L13" s="2" t="inlineStr">
+        <is>
+          <t>13717</t>
+        </is>
+      </c>
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>26805</t>
+        </is>
+      </c>
+      <c r="N13" s="2" t="inlineStr">
         <is>
           <t>11,28%</t>
         </is>
       </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>7,45%</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>15,05%</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>37</t>
-        </is>
-      </c>
-      <c r="K13" s="2" t="inlineStr">
-        <is>
-          <t>27340</t>
-        </is>
-      </c>
-      <c r="L13" s="2" t="inlineStr">
-        <is>
-          <t>19039</t>
-        </is>
-      </c>
-      <c r="M13" s="2" t="inlineStr">
-        <is>
-          <t>35418</t>
-        </is>
-      </c>
-      <c r="N13" s="2" t="inlineStr">
-        <is>
-          <t>15,78%</t>
-        </is>
-      </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>10,99%</t>
+          <t>7,92%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>20,45%</t>
+          <t>15,47%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -5726,12 +5726,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>37081</t>
+          <t>37875</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>58860</t>
+          <t>58718</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -5741,12 +5741,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>10,7%</t>
+          <t>10,93%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>16,99%</t>
+          <t>16,94%</t>
         </is>
       </c>
     </row>
@@ -5759,72 +5759,72 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>197</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>145890</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>137625</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>153143</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>84,22%</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>79,45%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>88,4%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
           <t>217</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="K14" s="2" t="inlineStr">
         <is>
           <t>153751</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>147222</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>160387</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>146496</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr">
+        <is>
+          <t>159584</t>
+        </is>
+      </c>
+      <c r="N14" s="2" t="inlineStr">
         <is>
           <t>88,72%</t>
         </is>
       </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>84,95%</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>92,55%</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>197</t>
-        </is>
-      </c>
-      <c r="K14" s="2" t="inlineStr">
-        <is>
-          <t>145890</t>
-        </is>
-      </c>
-      <c r="L14" s="2" t="inlineStr">
-        <is>
-          <t>137812</t>
-        </is>
-      </c>
-      <c r="M14" s="2" t="inlineStr">
-        <is>
-          <t>154191</t>
-        </is>
-      </c>
-      <c r="N14" s="2" t="inlineStr">
-        <is>
-          <t>84,22%</t>
-        </is>
-      </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>79,55%</t>
+          <t>84,53%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>89,01%</t>
+          <t>92,08%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -5839,12 +5839,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>287670</t>
+          <t>287812</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>309449</t>
+          <t>308655</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -5854,12 +5854,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>83,01%</t>
+          <t>83,06%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>89,3%</t>
+          <t>89,07%</t>
         </is>
       </c>
     </row>
@@ -5872,57 +5872,57 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
+          <t>234</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>173230</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>173230</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>173230</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
           <t>246</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
+      <c r="K15" s="2" t="inlineStr">
         <is>
           <t>173301</t>
         </is>
       </c>
-      <c r="E15" s="2" t="inlineStr">
+      <c r="L15" s="2" t="inlineStr">
         <is>
           <t>173301</t>
         </is>
       </c>
-      <c r="F15" s="2" t="inlineStr">
+      <c r="M15" s="2" t="inlineStr">
         <is>
           <t>173301</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>234</t>
-        </is>
-      </c>
-      <c r="K15" s="2" t="inlineStr">
-        <is>
-          <t>173230</t>
-        </is>
-      </c>
-      <c r="L15" s="2" t="inlineStr">
-        <is>
-          <t>173230</t>
-        </is>
-      </c>
-      <c r="M15" s="2" t="inlineStr">
-        <is>
-          <t>173230</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -5989,72 +5989,72 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>178</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>124527</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>107955</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>142338</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>16,74%</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>14,51%</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>19,13%</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
           <t>194</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="K16" s="2" t="inlineStr">
         <is>
           <t>124084</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>108595</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>140126</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
+      <c r="L16" s="2" t="inlineStr">
+        <is>
+          <t>108859</t>
+        </is>
+      </c>
+      <c r="M16" s="2" t="inlineStr">
+        <is>
+          <t>140183</t>
+        </is>
+      </c>
+      <c r="N16" s="2" t="inlineStr">
         <is>
           <t>17,62%</t>
         </is>
       </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>15,42%</t>
-        </is>
-      </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>19,89%</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>178</t>
-        </is>
-      </c>
-      <c r="K16" s="2" t="inlineStr">
-        <is>
-          <t>124527</t>
-        </is>
-      </c>
-      <c r="L16" s="2" t="inlineStr">
-        <is>
-          <t>108277</t>
-        </is>
-      </c>
-      <c r="M16" s="2" t="inlineStr">
-        <is>
-          <t>141691</t>
-        </is>
-      </c>
-      <c r="N16" s="2" t="inlineStr">
-        <is>
-          <t>16,74%</t>
-        </is>
-      </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>14,55%</t>
+          <t>15,45%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>19,04%</t>
+          <t>19,9%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -6069,12 +6069,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>224244</t>
+          <t>226452</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>271598</t>
+          <t>272633</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -6084,12 +6084,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>15,48%</t>
+          <t>15,63%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>18,75%</t>
+          <t>18,82%</t>
         </is>
       </c>
     </row>
@@ -6102,72 +6102,72 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
+          <t>886</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>619499</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>601688</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>636071</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>83,26%</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>80,87%</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>85,49%</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
           <t>867</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
+      <c r="K17" s="2" t="inlineStr">
         <is>
           <t>580287</t>
         </is>
       </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>564245</t>
-        </is>
-      </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>595776</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
+      <c r="L17" s="2" t="inlineStr">
+        <is>
+          <t>564188</t>
+        </is>
+      </c>
+      <c r="M17" s="2" t="inlineStr">
+        <is>
+          <t>595512</t>
+        </is>
+      </c>
+      <c r="N17" s="2" t="inlineStr">
         <is>
           <t>82,38%</t>
         </is>
       </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>80,11%</t>
-        </is>
-      </c>
-      <c r="I17" s="2" t="inlineStr">
-        <is>
-          <t>84,58%</t>
-        </is>
-      </c>
-      <c r="J17" s="2" t="inlineStr">
-        <is>
-          <t>886</t>
-        </is>
-      </c>
-      <c r="K17" s="2" t="inlineStr">
-        <is>
-          <t>619499</t>
-        </is>
-      </c>
-      <c r="L17" s="2" t="inlineStr">
-        <is>
-          <t>602335</t>
-        </is>
-      </c>
-      <c r="M17" s="2" t="inlineStr">
-        <is>
-          <t>635749</t>
-        </is>
-      </c>
-      <c r="N17" s="2" t="inlineStr">
-        <is>
-          <t>83,26%</t>
-        </is>
-      </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>80,96%</t>
+          <t>80,1%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>85,45%</t>
+          <t>84,55%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -6182,12 +6182,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>1176799</t>
+          <t>1175764</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>1224153</t>
+          <t>1221945</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -6197,12 +6197,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>81,25%</t>
+          <t>81,18%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>84,52%</t>
+          <t>84,37%</t>
         </is>
       </c>
     </row>
@@ -6215,57 +6215,57 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>1064</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>744026</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>744026</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>744026</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
           <t>1061</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
+      <c r="K18" s="2" t="inlineStr">
         <is>
           <t>704371</t>
         </is>
       </c>
-      <c r="E18" s="2" t="inlineStr">
+      <c r="L18" s="2" t="inlineStr">
         <is>
           <t>704371</t>
         </is>
       </c>
-      <c r="F18" s="2" t="inlineStr">
+      <c r="M18" s="2" t="inlineStr">
         <is>
           <t>704371</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J18" s="2" t="inlineStr">
-        <is>
-          <t>1064</t>
-        </is>
-      </c>
-      <c r="K18" s="2" t="inlineStr">
-        <is>
-          <t>744026</t>
-        </is>
-      </c>
-      <c r="L18" s="2" t="inlineStr">
-        <is>
-          <t>744026</t>
-        </is>
-      </c>
-      <c r="M18" s="2" t="inlineStr">
-        <is>
-          <t>744026</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -6385,7 +6385,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -6396,7 +6396,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -6564,72 +6564,72 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>10538</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>6896</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>14705</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>20,85%</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>13,65%</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>29,1%</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
           <t>29</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>15085</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>11085</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>20783</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>26,23%</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>19,27%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>36,14%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>22</t>
-        </is>
-      </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>13242</t>
+          <t>13426</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>8484</t>
+          <t>9665</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>19442</t>
+          <t>18667</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>21,55%</t>
+          <t>25,78%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>13,81%</t>
+          <t>18,56%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>31,64%</t>
+          <t>35,84%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -6639,32 +6639,32 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>28328</t>
+          <t>23964</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>21311</t>
+          <t>18436</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>36105</t>
+          <t>31062</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>23,81%</t>
+          <t>23,35%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>17,92%</t>
+          <t>17,96%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>30,35%</t>
+          <t>30,27%</t>
         </is>
       </c>
     </row>
@@ -6677,72 +6677,72 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>94</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>39999</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>35832</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>43641</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>79,15%</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>70,9%</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>86,35%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
           <t>80</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
-        <is>
-          <t>42426</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>36728</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>46426</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>73,77%</t>
-        </is>
-      </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>63,86%</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>80,73%</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>94</t>
-        </is>
-      </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>48202</t>
+          <t>38664</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>42002</t>
+          <t>33423</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>52960</t>
+          <t>42425</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>78,45%</t>
+          <t>74,22%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>68,36%</t>
+          <t>64,16%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>86,19%</t>
+          <t>81,44%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -6752,32 +6752,32 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>90627</t>
+          <t>78663</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>82850</t>
+          <t>71565</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>97644</t>
+          <t>84191</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>76,19%</t>
+          <t>76,65%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>69,65%</t>
+          <t>69,73%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>82,08%</t>
+          <t>82,04%</t>
         </is>
       </c>
     </row>
@@ -6790,57 +6790,57 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>116</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>50537</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>50537</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>50537</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
           <t>109</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
-        <is>
-          <t>57511</t>
-        </is>
-      </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>57511</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>57511</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>116</t>
-        </is>
-      </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>61444</t>
+          <t>52090</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>61444</t>
+          <t>52090</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>61444</t>
+          <t>52090</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -6865,17 +6865,17 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>118955</t>
+          <t>102627</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>118955</t>
+          <t>102627</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>118955</t>
+          <t>102627</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -6907,72 +6907,72 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>43</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>25694</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>18925</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>34632</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>16,31%</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>12,01%</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>21,99%</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
           <t>34</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
-        <is>
-          <t>22728</t>
-        </is>
-      </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>15788</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>32046</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
-        <is>
-          <t>14,27%</t>
-        </is>
-      </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>9,91%</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>20,12%</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>43</t>
-        </is>
-      </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>31277</t>
+          <t>20000</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>23305</t>
+          <t>14228</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>41606</t>
+          <t>27669</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>17,13%</t>
+          <t>13,74%</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>12,77%</t>
+          <t>9,78%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>22,79%</t>
+          <t>19,01%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -6982,32 +6982,32 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>54005</t>
+          <t>45694</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>43275</t>
+          <t>36554</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>66350</t>
+          <t>56714</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>15,8%</t>
+          <t>15,08%</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>12,66%</t>
+          <t>12,06%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>19,41%</t>
+          <t>18,72%</t>
         </is>
       </c>
     </row>
@@ -7020,72 +7020,72 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>233</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>131828</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>122890</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>138597</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>83,69%</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>78,01%</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>87,99%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
           <t>224</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
-        <is>
-          <t>136571</t>
-        </is>
-      </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>127253</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>143511</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>85,73%</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>79,88%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>90,09%</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>233</t>
-        </is>
-      </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>151277</t>
+          <t>125518</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>140948</t>
+          <t>117849</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>159249</t>
+          <t>131290</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>82,87%</t>
+          <t>86,26%</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>77,21%</t>
+          <t>80,99%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>87,23%</t>
+          <t>90,22%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -7095,32 +7095,32 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>287848</t>
+          <t>257345</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>275503</t>
+          <t>246325</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>298578</t>
+          <t>266485</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>84,2%</t>
+          <t>84,92%</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>80,59%</t>
+          <t>81,28%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>87,34%</t>
+          <t>87,94%</t>
         </is>
       </c>
     </row>
@@ -7133,57 +7133,57 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>276</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>157522</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>157522</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>157522</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
           <t>258</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
-        <is>
-          <t>159299</t>
-        </is>
-      </c>
-      <c r="E9" s="2" t="inlineStr">
-        <is>
-          <t>159299</t>
-        </is>
-      </c>
-      <c r="F9" s="2" t="inlineStr">
-        <is>
-          <t>159299</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>276</t>
-        </is>
-      </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>182554</t>
+          <t>145518</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>182554</t>
+          <t>145518</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>182554</t>
+          <t>145518</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -7208,17 +7208,17 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>341853</t>
+          <t>303039</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>341853</t>
+          <t>303039</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>341853</t>
+          <t>303039</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -7250,72 +7250,72 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>38</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>32225</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>23126</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>42399</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>16,1%</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>11,56%</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>21,19%</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
           <t>36</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
-        <is>
-          <t>25591</t>
-        </is>
-      </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>17635</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>34170</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>14,85%</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>10,23%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>19,83%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>38</t>
-        </is>
-      </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>34398</t>
+          <t>25764</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>24148</t>
+          <t>18129</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>46178</t>
+          <t>33741</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>16,19%</t>
+          <t>14,81%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>11,36%</t>
+          <t>10,42%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>21,73%</t>
+          <t>19,39%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -7325,32 +7325,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>59988</t>
+          <t>57989</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>46732</t>
+          <t>46070</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>73312</t>
+          <t>72129</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>15,59%</t>
+          <t>15,5%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>12,14%</t>
+          <t>12,31%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>19,05%</t>
+          <t>19,28%</t>
         </is>
       </c>
     </row>
@@ -7363,72 +7363,72 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>205</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>167901</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>157727</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>177000</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>83,9%</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>78,81%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>88,44%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
           <t>196</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
-        <is>
-          <t>146758</t>
-        </is>
-      </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>138179</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>154714</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
-        <is>
-          <t>85,15%</t>
-        </is>
-      </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>80,17%</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>89,77%</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>205</t>
-        </is>
-      </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>178092</t>
+          <t>148212</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>166312</t>
+          <t>140235</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>188342</t>
+          <t>155847</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>83,81%</t>
+          <t>85,19%</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>78,27%</t>
+          <t>80,61%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>88,64%</t>
+          <t>89,58%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -7438,32 +7438,32 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>324851</t>
+          <t>316113</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>311527</t>
+          <t>301973</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>338107</t>
+          <t>328032</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t>84,41%</t>
+          <t>84,5%</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>80,95%</t>
+          <t>80,72%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>87,86%</t>
+          <t>87,69%</t>
         </is>
       </c>
     </row>
@@ -7476,57 +7476,57 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>243</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>200126</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>200126</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>200126</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
           <t>232</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
-        <is>
-          <t>172349</t>
-        </is>
-      </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>172349</t>
-        </is>
-      </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>172349</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>243</t>
-        </is>
-      </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>212490</t>
+          <t>173976</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>212490</t>
+          <t>173976</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>212490</t>
+          <t>173976</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -7551,17 +7551,17 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>384839</t>
+          <t>374102</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>384839</t>
+          <t>374102</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>384839</t>
+          <t>374102</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -7593,72 +7593,72 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>43</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>37165</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>25504</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>48551</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>12,7%</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>8,72%</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>16,59%</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
           <t>50</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
-        <is>
-          <t>39831</t>
-        </is>
-      </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>27373</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>58827</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
-        <is>
-          <t>14,46%</t>
-        </is>
-      </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>9,94%</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>21,36%</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>43</t>
-        </is>
-      </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>37921</t>
+          <t>36597</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>28203</t>
+          <t>28157</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>51951</t>
+          <t>47950</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>12,41%</t>
+          <t>14,26%</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>9,23%</t>
+          <t>10,98%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>17,01%</t>
+          <t>18,69%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -7668,32 +7668,32 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>77752</t>
+          <t>73762</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>60603</t>
+          <t>60483</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>98741</t>
+          <t>90568</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>13,38%</t>
+          <t>13,43%</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>10,43%</t>
+          <t>11,01%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>17,0%</t>
+          <t>16,49%</t>
         </is>
       </c>
     </row>
@@ -7706,72 +7706,72 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>299</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>255480</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>244094</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>267141</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>87,3%</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>83,41%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>91,28%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
           <t>292</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
-        <is>
-          <t>235627</t>
-        </is>
-      </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>216631</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>248085</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
-        <is>
-          <t>85,54%</t>
-        </is>
-      </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>78,64%</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>90,06%</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>299</t>
-        </is>
-      </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>267562</t>
+          <t>219956</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>253532</t>
+          <t>208603</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>277280</t>
+          <t>228396</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>87,59%</t>
+          <t>85,74%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>82,99%</t>
+          <t>81,31%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>90,77%</t>
+          <t>89,02%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -7781,32 +7781,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>503188</t>
+          <t>475436</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>482199</t>
+          <t>458630</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>520337</t>
+          <t>488715</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>86,62%</t>
+          <t>86,57%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>83,0%</t>
+          <t>83,51%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>89,57%</t>
+          <t>88,99%</t>
         </is>
       </c>
     </row>
@@ -7824,17 +7824,17 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>275458</t>
+          <t>292645</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>275458</t>
+          <t>292645</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>275458</t>
+          <t>292645</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -7859,17 +7859,17 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>305483</t>
+          <t>256553</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>305483</t>
+          <t>256553</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>305483</t>
+          <t>256553</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -7894,17 +7894,17 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>580940</t>
+          <t>549198</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>580940</t>
+          <t>549198</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>580940</t>
+          <t>549198</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -7936,72 +7936,72 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>146</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>105622</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>90588</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>125160</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>15,07%</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>12,93%</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>17,86%</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
           <t>149</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
-        <is>
-          <t>103235</t>
-        </is>
-      </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>84008</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>124638</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
-        <is>
-          <t>15,53%</t>
-        </is>
-      </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>12,64%</t>
-        </is>
-      </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>18,75%</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>146</t>
-        </is>
-      </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>116838</t>
+          <t>95788</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>99617</t>
+          <t>81393</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>135313</t>
+          <t>111298</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>15,33%</t>
+          <t>15,25%</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>13,07%</t>
+          <t>12,96%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>17,76%</t>
+          <t>17,72%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -8011,32 +8011,32 @@
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>220073</t>
+          <t>201409</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>194422</t>
+          <t>176479</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>251730</t>
+          <t>226552</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
-          <t>15,43%</t>
+          <t>15,16%</t>
         </is>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>13,63%</t>
+          <t>13,28%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>17,65%</t>
+          <t>17,05%</t>
         </is>
       </c>
     </row>
@@ -8049,72 +8049,72 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
+          <t>831</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>595207</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>575669</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>610241</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>84,93%</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>82,14%</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>87,07%</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
           <t>792</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
-        <is>
-          <t>561382</t>
-        </is>
-      </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>539979</t>
-        </is>
-      </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>580609</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
-        <is>
-          <t>84,47%</t>
-        </is>
-      </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>81,25%</t>
-        </is>
-      </c>
-      <c r="I17" s="2" t="inlineStr">
-        <is>
-          <t>87,36%</t>
-        </is>
-      </c>
-      <c r="J17" s="2" t="inlineStr">
-        <is>
-          <t>831</t>
-        </is>
-      </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>645134</t>
+          <t>532349</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>626659</t>
+          <t>516839</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>662355</t>
+          <t>546744</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>84,67%</t>
+          <t>84,75%</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>82,24%</t>
+          <t>82,28%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>86,93%</t>
+          <t>87,04%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -8124,32 +8124,32 @@
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>1206516</t>
+          <t>1127557</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>1174859</t>
+          <t>1102414</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>1232167</t>
+          <t>1152487</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
         <is>
-          <t>84,57%</t>
+          <t>84,84%</t>
         </is>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>82,35%</t>
+          <t>82,95%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>86,37%</t>
+          <t>86,72%</t>
         </is>
       </c>
     </row>
@@ -8162,57 +8162,57 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>977</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>700829</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>700829</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>700829</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
           <t>941</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
-        <is>
-          <t>664617</t>
-        </is>
-      </c>
-      <c r="E18" s="2" t="inlineStr">
-        <is>
-          <t>664617</t>
-        </is>
-      </c>
-      <c r="F18" s="2" t="inlineStr">
-        <is>
-          <t>664617</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J18" s="2" t="inlineStr">
-        <is>
-          <t>977</t>
-        </is>
-      </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>761972</t>
+          <t>628137</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>761972</t>
+          <t>628137</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>761972</t>
+          <t>628137</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -8237,17 +8237,17 @@
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>1426589</t>
+          <t>1328966</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>1426589</t>
+          <t>1328966</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>1426589</t>
+          <t>1328966</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
